--- a/output/pdf_financials_xlsx/PSYC.xlsx
+++ b/output/pdf_financials_xlsx/PSYC.xlsx
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>1.465853</v>
+        <v>7.821622</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.722425</v>
+        <v>7.060872</v>
       </c>
       <c r="D92" s="1" t="inlineStr">
         <is>
@@ -3272,7 +3272,11 @@
           <t>Reserve for warrants 14</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>6.355769</v>
       </c>

--- a/output/pdf_financials_xlsx/PSYC.xlsx
+++ b/output/pdf_financials_xlsx/PSYC.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.169821</v>
+        <v>3.597942</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.075255</v>
+        <v>4.761383</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.999414</v>
+        <v>5.274716</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.285572</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.145041</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-3.433337</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.259766</v>
+        <v>-4.545338</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.035588</v>
+        <v>-5.180629</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-3.433337</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.259766</v>
+        <v>-4.545338</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.035588</v>
+        <v>-5.180629</v>
       </c>
     </row>
     <row r="30">
@@ -912,10 +912,10 @@
         <v>-1069.255612028801</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-683.5793926400452</v>
+        <v>-729.4061198159048</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-1066.179690113529</v>
+        <v>-1096.889066741195</v>
       </c>
     </row>
     <row r="31">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>-3.597942</v>
+        <v>3.597942</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>-4.761383</v>
+        <v>4.761383</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-5.274716</v>
+        <v>5.274716</v>
       </c>
     </row>
     <row r="64">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">

--- a/output/pdf_financials_xlsx/PSYC.xlsx
+++ b/output/pdf_financials_xlsx/PSYC.xlsx
@@ -1508,15 +1508,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.13922</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.292855</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.5052680000000001</v>
       </c>
     </row>
     <row r="65">
@@ -1562,15 +1560,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.162361</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.156474</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.12732</v>
       </c>
     </row>
     <row r="68">
